--- a/data/LCI/LCI_review.xlsx
+++ b/data/LCI/LCI_review.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/LCI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="11_AD4D9D64A577C15A4A5418A680D85C6E5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A784B287-757D-4FB3-BACC-093B14B1FDD3}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="11_AD4D9D64A577C15A4A5418A680D85C6E5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1275C583-1CBE-46C5-BF22-5656C57A1789}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
     <sheet name="data" sheetId="1" r:id="rId2"/>
+    <sheet name="Cu_Sanjuan-Delmás" sheetId="4" r:id="rId3"/>
+    <sheet name="Ni_Roy" sheetId="5" r:id="rId4"/>
+    <sheet name="Cu_GREET" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$M$108</definedName>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="313">
   <si>
     <t>IMPORTED_FROM</t>
   </si>
@@ -1046,6 +1049,12 @@
   </si>
   <si>
     <t>Not mentionned</t>
+  </si>
+  <si>
+    <t>Operation data from 2015</t>
+  </si>
+  <si>
+    <t>Economic allocation for smelting part</t>
   </si>
 </sst>
 </file>
@@ -1436,8 +1445,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" customWidth="1"/>
-    <col min="3" max="3" width="46.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="73.36328125" customWidth="1"/>
     <col min="5" max="5" width="35.1796875" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
@@ -4442,6 +4451,12 @@
       <c r="I105" t="s">
         <v>17</v>
       </c>
+      <c r="J105" t="s">
+        <v>311</v>
+      </c>
+      <c r="K105" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
@@ -4467,6 +4482,12 @@
       </c>
       <c r="I106" t="s">
         <v>17</v>
+      </c>
+      <c r="J106" t="s">
+        <v>311</v>
+      </c>
+      <c r="K106" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
@@ -4536,4 +4557,31 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF0DE555-1B21-4A5B-860A-52FEF714FA71}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D0436B5-16D6-455F-92F9-B0385EAA91BA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4EEDB92-F178-4A58-B65C-DF0454A4BD40}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>